--- a/Base de donnees a mettre a jour.xlsx
+++ b/Base de donnees a mettre a jour.xlsx
@@ -80,33 +80,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6893,17 +6877,17 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" style="11" min="1" max="1"/>
+    <col width="18" customWidth="1" style="11" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Indicateur</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
